--- a/results/Int Task Remove ACC -0.8/Rando_5_permute.xlsx
+++ b/results/Int Task Remove ACC -0.8/Rando_5_permute.xlsx
@@ -440,527 +440,527 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6297109182084644</v>
+        <v>0.6238188388862453</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6317645758660205</v>
+        <v>0.6248799833314094</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6289872986465217</v>
+        <v>0.624247872079829</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6382511072505554</v>
+        <v>0.6232243868239296</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6635288701680093</v>
+        <v>0.6274985288279334</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6626183624799034</v>
+        <v>0.6272201323914077</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6596837613575891</v>
+        <v>0.6449554988047607</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6515053820964695</v>
+        <v>0.6484845519893907</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6469084973209183</v>
+        <v>0.6550988430533929</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6539813858018522</v>
+        <v>0.6547627259903311</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6454894146002212</v>
+        <v>0.6412099932706197</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6433442486323027</v>
+        <v>0.641021697324297</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6433442486323027</v>
+        <v>0.6383359284151605</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6413725964990329</v>
+        <v>0.6430014444234835</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6383693641439467</v>
+        <v>0.6309631742402698</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6413416244555256</v>
+        <v>0.6436983154023972</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6421701266193451</v>
+        <v>0.6384316601860012</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6409812224947137</v>
+        <v>0.6242644139667022</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6661379128784573</v>
+        <v>0.6335025298528265</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6552938261454728</v>
+        <v>0.6406440495665322</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6552938261454728</v>
+        <v>0.6310831909088606</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6552938261454728</v>
+        <v>0.6325290222125866</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6603278390805245</v>
+        <v>0.6389268609270777</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6537054530506055</v>
+        <v>0.6421278920145626</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6567382496290394</v>
+        <v>0.6527850906213837</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6666866107855918</v>
+        <v>0.6596925602335855</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6491905737993405</v>
+        <v>0.6641025568829735</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6526524035713582</v>
+        <v>0.6702649376758016</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6557376414507305</v>
+        <v>0.662354044244972</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6556623230722014</v>
+        <v>0.662354044244972</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.681868191429754</v>
+        <v>0.6285941648670033</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6812360801781737</v>
+        <v>0.6287757736675685</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6710321996626862</v>
+        <v>0.6239515259362709</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6633176971440961</v>
+        <v>0.6263831833066317</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6636337527698861</v>
+        <v>0.6012951241556599</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6611605647048223</v>
+        <v>0.5945974197472118</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6625525468874504</v>
+        <v>0.5985463552943893</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6544966479802004</v>
+        <v>0.5968101610827827</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6516521473480892</v>
+        <v>0.5956360390698251</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6519682029738794</v>
+        <v>0.5956360390698251</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6271666352253498</v>
+        <v>0.5952446650655059</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.63079247604594</v>
+        <v>0.5931223761751778</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6010216550896923</v>
+        <v>0.5487605551316452</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6078094599883432</v>
+        <v>0.5586416928755853</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5721004535996553</v>
+        <v>0.559070726069169</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5536815904989033</v>
+        <v>0.5682592162946737</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5198034542275431</v>
+        <v>0.538960367046872</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5237467584940829</v>
+        <v>0.5408042595006743</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5237467584940829</v>
+        <v>0.568506640687692</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5333104327920735</v>
+        <v>0.5621573717687007</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.538665780678513</v>
+        <v>0.5495003646254213</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5448281614713411</v>
+        <v>0.5359557268716265</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5417038565825447</v>
+        <v>0.5472517238757852</v>
       </c>
     </row>
     <row r="55">
@@ -970,37 +970,37 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5531061440087398</v>
+        <v>0.5474533941136224</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5581697211671393</v>
+        <v>0.5499818391199435</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5609913447216599</v>
+        <v>0.5488305941845765</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5609913447216599</v>
+        <v>0.5572644928046312</v>
       </c>
     </row>
     <row r="59">
@@ -1010,317 +1010,317 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5419889401648276</v>
+        <v>0.5581669055268204</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5614393834873959</v>
+        <v>0.555391036127481</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5507702184092196</v>
+        <v>0.5405916786566016</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.517411567776686</v>
+        <v>0.5336250805977041</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5305423064036108</v>
+        <v>0.5283369561238769</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5390004899214155</v>
+        <v>0.5283369561238769</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5429842690175386</v>
+        <v>0.5291721454334537</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5298887258945993</v>
+        <v>0.5265993540921109</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5192649630165644</v>
+        <v>0.5253727907782149</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5225237147305855</v>
+        <v>0.527901235784536</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5127421802629245</v>
+        <v>0.5376060440535084</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5224051058821542</v>
+        <v>0.5376060440535084</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5630837174336002</v>
+        <v>0.5379220996792986</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5784722476411973</v>
+        <v>0.5278502023037569</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.564330342184768</v>
+        <v>0.510640656719948</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.564330342184768</v>
+        <v>0.4932199381122258</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5511594806832996</v>
+        <v>0.4915562466388294</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5584421343679873</v>
+        <v>0.4792086079755827</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5513959944700824</v>
+        <v>0.4876815736050614</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.572602693441529</v>
+        <v>0.4916854141384563</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5757122162186514</v>
+        <v>0.4952992884876914</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.602518871829237</v>
+        <v>0.4967035890967144</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6207948411838078</v>
+        <v>0.4967035890967144</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5530002055417432</v>
+        <v>0.4967035890967144</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5508726373258175</v>
+        <v>0.4967035890967144</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5233437699734484</v>
+        <v>0.4975993146731464</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5231311891293758</v>
+        <v>0.4972832590473562</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5324326569226741</v>
+        <v>0.4972832590473562</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5096147077787695</v>
+        <v>0.4961091370343987</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5117074324457496</v>
+        <v>0.4954393665935539</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5164521383380402</v>
+        <v>0.4970573039117691</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4897003877136719</v>
+        <v>0.4975239962946174</v>
       </c>
     </row>
   </sheetData>
